--- a/data/trans_camb/P57_AF_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P57_AF_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 3,73</t>
+          <t>-4,17; 4,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 12,3</t>
+          <t>4,23; 12,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 0,38</t>
+          <t>-8,99; 0,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 5,59</t>
+          <t>-1,17; 6,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,95; 17,1</t>
+          <t>9,88; 16,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 2,04</t>
+          <t>-4,8; 2,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,91</t>
+          <t>-1,61; 3,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,48; 14,02</t>
+          <t>8,26; 14,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 0,38</t>
+          <t>-5,41; 0,27</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 5,7</t>
+          <t>-6,05; 6,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 19,04</t>
+          <t>6,19; 19,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 0,56</t>
+          <t>-13,27; 0,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 8,45</t>
+          <t>-1,72; 9,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,54; 26,21</t>
+          <t>14,34; 25,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 3,1</t>
+          <t>-7,02; 4,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 5,85</t>
+          <t>-2,33; 5,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,31; 21,27</t>
+          <t>11,99; 21,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 0,58</t>
+          <t>-7,87; 0,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 5,6</t>
+          <t>-1,14; 5,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,68; 20,31</t>
+          <t>14,1; 20,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-27,06; -1,41</t>
+          <t>-27,03; -1,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 12,04</t>
+          <t>5,09; 11,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,42; 20,85</t>
+          <t>14,73; 21,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 11,59</t>
+          <t>-7,46; 10,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,47</t>
+          <t>2,48; 7,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,27; 19,81</t>
+          <t>15,08; 19,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 1,85</t>
+          <t>-12,41; 1,74</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 9,98</t>
+          <t>-1,85; 9,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,7; 36,33</t>
+          <t>23,42; 36,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-45,39; -2,39</t>
+          <t>-45,89; -2,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 21,05</t>
+          <t>8,42; 20,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,83; 37,05</t>
+          <t>24,09; 37,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 20,21</t>
+          <t>-12,54; 18,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,16</t>
+          <t>4,11; 12,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,53; 34,91</t>
+          <t>25,09; 34,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 3,15</t>
+          <t>-21,01; 3,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 8,82</t>
+          <t>-5,06; 8,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 15,96</t>
+          <t>4,13; 16,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 1,21</t>
+          <t>-11,54; 0,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 11,77</t>
+          <t>-0,91; 12,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,77; 19,23</t>
+          <t>7,49; 19,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 1,19</t>
+          <t>-9,84; 1,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 7,93</t>
+          <t>-1,85; 8,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,48; 16,18</t>
+          <t>7,2; 15,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,52; -0,71</t>
+          <t>-9,59; -0,98</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 16,66</t>
+          <t>-8,41; 15,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,42; 29,89</t>
+          <t>7,18; 31,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 2,28</t>
+          <t>-19,43; 0,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 24,26</t>
+          <t>-1,28; 26,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,19; 39,73</t>
+          <t>13,41; 39,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 2,56</t>
+          <t>-17,42; 4,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 15,44</t>
+          <t>-3,31; 15,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,9; 31,43</t>
+          <t>12,62; 30,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,41; -1,34</t>
+          <t>-16,94; -1,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,73</t>
+          <t>-1,47; 3,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,18; 15,55</t>
+          <t>10,62; 15,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,31; -3,92</t>
+          <t>-20,56; -3,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,83</t>
+          <t>3,17; 8,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,37; 16,94</t>
+          <t>12,47; 17,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 4,59</t>
+          <t>-7,07; 4,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,09</t>
+          <t>1,72; 5,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,4; 15,56</t>
+          <t>12,54; 15,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,87; -1,8</t>
+          <t>-11,5; -1,59</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 6,31</t>
+          <t>-2,38; 6,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,03; 26,23</t>
+          <t>17,06; 26,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,92; -6,45</t>
+          <t>-33,83; -6,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,67; 13,12</t>
+          <t>5,04; 13,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,7; 28,26</t>
+          <t>19,93; 28,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 7,56</t>
+          <t>-11,4; 6,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,44</t>
+          <t>2,8; 8,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,08; 25,81</t>
+          <t>20,24; 26,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-19,42; -2,97</t>
+          <t>-18,71; -2,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_AF_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P57_AF_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,32</t>
+          <t>-3,86</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-0,63</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,63</t>
+          <t>-1,97</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 4,06</t>
+          <t>-4,86; 3,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 12,57</t>
+          <t>4,1; 12,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 0,7</t>
+          <t>-8,77; 0,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 6,13</t>
+          <t>-1,18; 5,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,88; 16,88</t>
+          <t>10,07; 17,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 2,64</t>
+          <t>-4,2; 2,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,91</t>
+          <t>-1,78; 3,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,26; 14,05</t>
+          <t>8,44; 14,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 0,27</t>
+          <t>-5,0; 0,8</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-6,44%</t>
+          <t>-5,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-2,19%</t>
+          <t>-0,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-3,91%</t>
+          <t>-2,93%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 6,28</t>
+          <t>-6,98; 5,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 19,4</t>
+          <t>5,98; 19,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 0,87</t>
+          <t>-12,91; 1,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 9,3</t>
+          <t>-1,68; 9,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,34; 25,77</t>
+          <t>14,46; 27,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 4,03</t>
+          <t>-6,16; 4,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 5,96</t>
+          <t>-2,59; 6,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,99; 21,39</t>
+          <t>12,23; 21,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 0,4</t>
+          <t>-7,3; 1,24</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-8,5</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,28</t>
+          <t>-0,74</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,57</t>
+          <t>-1,03; 5,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,1; 20,38</t>
+          <t>14,05; 20,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-27,03; -1,43</t>
+          <t>-4,53; 2,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 11,67</t>
+          <t>4,76; 11,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,73; 21,13</t>
+          <t>14,65; 20,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 10,38</t>
+          <t>-3,8; 2,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,47</t>
+          <t>2,77; 7,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,08; 19,79</t>
+          <t>15,45; 19,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 1,74</t>
+          <t>-3,2; 1,55</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-14,64%</t>
+          <t>-1,6%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>-0,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-7,32%</t>
+          <t>-1,27%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 9,86</t>
+          <t>-1,68; 9,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,42; 36,25</t>
+          <t>23,19; 35,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-45,89; -2,56</t>
+          <t>-7,51; 4,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,42; 20,39</t>
+          <t>7,76; 19,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,09; 37,01</t>
+          <t>24,03; 36,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 18,25</t>
+          <t>-6,26; 4,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 12,99</t>
+          <t>4,6; 12,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,09; 34,9</t>
+          <t>25,82; 34,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 3,0</t>
+          <t>-5,35; 2,66</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-5,5</t>
+          <t>-5,59</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,46</t>
+          <t>-3,77</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-5,18</t>
+          <t>-4,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 8,19</t>
+          <t>-5,09; 8,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 16,57</t>
+          <t>3,44; 15,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 0,28</t>
+          <t>-12,03; 0,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 12,37</t>
+          <t>-1,66; 11,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,49; 19,45</t>
+          <t>6,61; 19,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 1,89</t>
+          <t>-9,49; 2,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 8,05</t>
+          <t>-1,29; 8,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 15,75</t>
+          <t>7,21; 15,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,59; -0,98</t>
+          <t>-8,94; -0,88</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-9,69%</t>
+          <t>-9,86%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-8,63%</t>
+          <t>-7,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-9,53%</t>
+          <t>-8,98%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 15,39</t>
+          <t>-8,7; 15,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,18; 31,74</t>
+          <t>5,72; 30,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 0,59</t>
+          <t>-20,09; 0,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 26,35</t>
+          <t>-2,59; 24,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,41; 39,91</t>
+          <t>12,2; 40,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 4,19</t>
+          <t>-17,37; 4,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 15,44</t>
+          <t>-2,21; 15,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,62; 30,56</t>
+          <t>12,66; 30,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,94; -1,95</t>
+          <t>-15,72; -1,62</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-8,85</t>
+          <t>-3,77</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-3,07</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,82</t>
+          <t>-3,41</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,56</t>
+          <t>-1,21; 3,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,62; 15,51</t>
+          <t>11,04; 15,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,56; -3,63</t>
+          <t>-6,23; -1,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,04</t>
+          <t>3,32; 7,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,47; 17,13</t>
+          <t>12,63; 17,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 4,18</t>
+          <t>-5,25; -0,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,08</t>
+          <t>1,59; 5,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,54; 15,74</t>
+          <t>12,45; 15,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,5; -1,59</t>
+          <t>-5,06; -1,62</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-14,59%</t>
+          <t>-6,21%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-4,84%</t>
+          <t>-5,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-9,55%</t>
+          <t>-5,59%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 6,03</t>
+          <t>-1,98; 5,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,06; 26,02</t>
+          <t>17,79; 26,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,83; -6,1</t>
+          <t>-10,14; -2,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,04; 13,44</t>
+          <t>5,34; 13,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,93; 28,7</t>
+          <t>20,21; 28,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 6,91</t>
+          <t>-8,49; -1,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,46</t>
+          <t>2,58; 8,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,24; 26,34</t>
+          <t>20,11; 26,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-18,71; -2,62</t>
+          <t>-8,14; -2,65</t>
         </is>
       </c>
     </row>
